--- a/docs/freigabe-katalog/versand-2026-10-25-steuern-gobd/Betriebsklar-Fachfragen-GoBD-Zugriff-ohne-Abo-Steuerberater.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-steuern-gobd/Betriebsklar-Fachfragen-GoBD-Zugriff-ohne-Abo-Steuerberater.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -475,7 +475,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -560,20 +559,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Bestätigt (Name, Datum):</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Unterschrift:</t>
+          <t>Bitte bestätigen Sie Ihre Antworten per E-Mail (Antwort auf unsere Mail, mit dieser Datei im Anhang); eine Unterschrift ist nicht nötig.</t>
         </is>
       </c>
     </row>
